--- a/Three Statement Models/3 statement financial model.xlsx
+++ b/Three Statement Models/3 statement financial model.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lizzie\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lizzie\OneDrive\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7640" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6390"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="6" r:id="rId1"/>
@@ -3441,15 +3441,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A11B45D48646B844BCF67175E7EDD4C7" ma:contentTypeVersion="25" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="33f624f548c30d8243a9fd905e457e0a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6423d52d-cc33-4d55-a30a-79dd6b3aa391" xmlns:ns3="01961662-24f8-48fa-8e1b-d6aec199e9f1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6a5d9e74c8d8c82d092558e57a41c457" ns2:_="" ns3:_="">
     <xsd:import namespace="6423d52d-cc33-4d55-a30a-79dd6b3aa391"/>
@@ -3752,15 +3743,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A4DB5-C5C4-443F-87B2-80C3CEDDC259}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA772FDE-7B67-405C-912F-79931FAB6E2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3777,4 +3769,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A4DB5-C5C4-443F-87B2-80C3CEDDC259}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>